--- a/data/trans_dic/P19C10_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P19C10_2023-Estudios-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo motivo por su última visita al dentista fue por dolor de mandíbula / solo 2023</t>
+          <t>Población cuyo motivo por su última visita al dentista fue por dolor de mandíbula / solo 2023 (tasa de respuesta: 99,54%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,3</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,7; 1,9</t>
+          <t>0,7; 1,92</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,43; 1,17</t>
+          <t>0,45; 1,19</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,14; 0,74</t>
+          <t>0,15; 0,75</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -632,7 +632,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,17; 0,54</t>
+          <t>0,17; 0,55</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,68</t>
+          <t>0,0; 1,79</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,29; 1,7</t>
+          <t>0,32; 1,66</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,26; 1,16</t>
+          <t>0,26; 1,17</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,12; 0,58</t>
+          <t>0,14; 0,57</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,37; 0,82</t>
+          <t>0,37; 0,79</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,3; 0,61</t>
+          <t>0,31; 0,63</t>
         </is>
       </c>
     </row>
@@ -774,7 +774,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo motivo por su última visita al dentista fue por dolor de mandíbula / solo 2023</t>
+          <t>Población cuyo motivo por su última visita al dentista fue por dolor de mandíbula / solo 2023 (tasa de respuesta: 99,54%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 1433</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>5064; 13736</t>
+          <t>5087; 13865</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5167; 14139</t>
+          <t>5397; 14324</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3141; 16454</t>
+          <t>3308; 16774</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2554; 12240</t>
+          <t>2570; 12259</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7551; 23971</t>
+          <t>7567; 24454</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 10626</t>
+          <t>0; 11305</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1882; 11065</t>
+          <t>2072; 10834</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3379; 14858</t>
+          <t>3335; 14976</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4163; 19329</t>
+          <t>4726; 19141</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>13042; 29245</t>
+          <t>13155; 28363</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>20443; 42137</t>
+          <t>21643; 43409</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P19C10_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P19C10_2023-Estudios-trans_dic.xlsx
@@ -554,12 +554,12 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,79%</t>
         </is>
       </c>
     </row>
@@ -577,12 +577,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,7; 1,92</t>
+          <t>0,81; 2,13</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,45; 1,19</t>
+          <t>0,47; 1,29</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,36%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,15; 0,75</t>
+          <t>0,16; 0,79</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,12; 0,56</t>
+          <t>0,16; 0,65</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,17; 0,55</t>
+          <t>0,21; 0,61</t>
         </is>
       </c>
     </row>
@@ -649,12 +649,12 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,79</t>
+          <t>0,0; 1,51</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,32; 1,66</t>
+          <t>0,35; 1,63</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,26; 1,17</t>
+          <t>0,27; 1,15</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,48%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,14; 0,57</t>
+          <t>0,15; 0,57</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,37; 0,79</t>
+          <t>0,44; 0,88</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,31; 0,63</t>
+          <t>0,34; 0,66</t>
         </is>
       </c>
     </row>
@@ -861,12 +861,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>8902</t>
+          <t>10489</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8902</t>
+          <t>10489</t>
         </is>
       </c>
     </row>
@@ -884,12 +884,12 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>5087; 13865</t>
+          <t>6318; 16725</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5397; 14324</t>
+          <t>6251; 17052</t>
         </is>
       </c>
     </row>
@@ -929,17 +929,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>8157</t>
+          <t>8413</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>5854</t>
+          <t>6920</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>14011</t>
+          <t>15333</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3308; 16774</t>
+          <t>3511; 16945</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2570; 12259</t>
+          <t>3404; 13768</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7567; 24454</t>
+          <t>9000; 26036</t>
         </is>
       </c>
     </row>
@@ -1002,17 +1002,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2120</t>
+          <t>2342</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5106</t>
+          <t>5576</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7225</t>
+          <t>7917</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 11305</t>
+          <t>0; 10567</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2072; 10834</t>
+          <t>2522; 11821</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3335; 14976</t>
+          <t>3908; 16393</t>
         </is>
       </c>
     </row>
@@ -1075,17 +1075,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>10277</t>
+          <t>10755</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>19862</t>
+          <t>22984</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>30139</t>
+          <t>33739</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4726; 19141</t>
+          <t>5174; 19253</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>13155; 28363</t>
+          <t>15816; 31750</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>21643; 43409</t>
+          <t>23964; 46275</t>
         </is>
       </c>
     </row>
